--- a/docs/novamart-demo-runsheet.xlsx
+++ b/docs/novamart-demo-runsheet.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="170">
   <si>
     <t xml:space="preserve">NovaMart — live demo run sheet</t>
   </si>
@@ -459,52 +459,82 @@
     <t xml:space="preserve">How to run the demo</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Start the app on the real crew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHAT_ENGINE=sdk AS_OF_DATE=2026-09-01 SDK_STREAM_MODE=live OPERATOR_KEY=demo-secret npm run dev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Open the demo picker</t>
+    <t xml:space="preserve">Full demo — one command</t>
+  </si>
+  <si>
+    <t xml:space="preserve">npm run demo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It prints where to look, then starts the app. Opens on:</t>
   </si>
   <si>
     <t xml:space="preserve">http://localhost:3000/?demo=1</t>
   </si>
   <si>
-    <t xml:space="preserve">Each chip fills the order id and the question. You still press Run.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chips are tinted by expected outcome: green resolved, violet escalated, amber needs-input.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Confirm you are on the crew, not the keyless fallback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">curl -s localhost:3000/api/health   →   "engine":"sdk"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. After the demo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">npm run observability      what it cost, latency, error rate</t>
+    <t xml:space="preserve">What to have open on screen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The app          http://localhost:3000/?demo=1   (add &amp;trace=1 for the hop panel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Arize            https://app.arize.com  -&gt;  project novamart-support-crew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. The outbox       data/outbox.md   grows with every handoff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. A ticket packet  data/tickets/&lt;STUB-ID&gt;.md   what the human receives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehearse for free</t>
+  </si>
+  <si>
+    <t xml:space="preserve">npm run dev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same UI, same picker, same ticket and outbox artifacts — no crew, no API usage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escalation is structural on both engines, so the handoff artifacts still appear.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirm you are on the crew before you start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">curl -s localhost:3000/api/health    -&gt;    "engine":"sdk"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After the demo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">npm run observability      run rate, error rate, latency, TTFT, cost by agent path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">npm run prune:traces       sweep trace logs and handoff artifacts (7-day window)</t>
   </si>
   <si>
     <t xml:space="preserve">Notes</t>
   </si>
   <si>
-    <t xml:space="preserve">SDK_STREAM_MODE=live matters. The default (final) shows nothing for 10-16s then dumps the</t>
-  </si>
-  <si>
-    <t xml:space="preserve">whole answer at once; live streams it as it is written.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost is roughly $0.20-0.25 per turn, so all 23 is about $6.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pin AS_OF_DATE to 2026-09-01 or the day counts in the run sheet stop matching the screen.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The picker lists real order ids — keep it off for anything customer-facing.</t>
+    <t xml:space="preserve">Each crew turn is a real model call. A full 23-scenario pass is roughly $4-6 of usage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDK_STREAM_MODE=live is set by the script. The default (final) shows nothing for 10-16s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">then dumps the whole answer at once — much worse to watch.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep AS_OF_DATE=2026-09-01 or the day counts in the Run sheet stop matching the screen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arize traces appear a few seconds AFTER a turn finishes — spans are replayed at turn end,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">so do not switch to the Arize tab until the answer is on screen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The picker lists real order ids. Keep it off for anything customer-facing.</t>
   </si>
 </sst>
 </file>
@@ -2273,7 +2303,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr defaultColWidth="8.515625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="108"/>
@@ -2298,7 +2328,7 @@
       <c r="A5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2311,26 +2341,28 @@
       <c r="A8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="12" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="12" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13"/>
+      <c r="A11" s="12" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="17" t="s">
-        <v>151</v>
+      <c r="A13" s="12" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2338,45 +2370,96 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13"/>
+      <c r="A17" s="13" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="s">
-        <v>154</v>
+      <c r="A18" s="13" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
-        <v>155</v>
-      </c>
+      <c r="A19" s="13"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
-        <v>156</v>
+      <c r="A20" s="12" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
-        <v>157</v>
+      <c r="A21" s="17" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="s">
-        <v>158</v>
-      </c>
+      <c r="A22" s="13"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="12" t="s">
         <v>159</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="17" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="17" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="13"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="12" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="13" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="13" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="13" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="13" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
